--- a/artfynd/A 62998-2025 artfynd.xlsx
+++ b/artfynd/A 62998-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1626,6 +1626,1277 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>130236817</v>
+      </c>
+      <c r="B10" t="n">
+        <v>5177</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>631422</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6663828</v>
+      </c>
+      <c r="S10" t="n">
+        <v>15</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>130236804</v>
+      </c>
+      <c r="B11" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>631498</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6663817</v>
+      </c>
+      <c r="S11" t="n">
+        <v>15</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>130236802</v>
+      </c>
+      <c r="B12" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>631483</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6663930</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Flykt och lockläte</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>130236801</v>
+      </c>
+      <c r="B13" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>631418</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6663846</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>130236752</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>53</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>631701</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6663882</v>
+      </c>
+      <c r="S14" t="n">
+        <v>15</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>130236815</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96322</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>631419</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6663842</v>
+      </c>
+      <c r="S15" t="n">
+        <v>15</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>130236800</v>
+      </c>
+      <c r="B16" t="n">
+        <v>97079</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>53</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>631428</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6663768</v>
+      </c>
+      <c r="S16" t="n">
+        <v>15</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>130236805</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>631493</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6663935</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>130236810</v>
+      </c>
+      <c r="B18" t="n">
+        <v>105900</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>631475</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6663922</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>130236808</v>
+      </c>
+      <c r="B19" t="n">
+        <v>98833</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>631477</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6663923</v>
+      </c>
+      <c r="S19" t="n">
+        <v>15</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>18 buketter</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>130236809</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91023</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>631421</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6663766</v>
+      </c>
+      <c r="S20" t="n">
+        <v>15</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>130236806</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>631465</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6663897</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>130236807</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57738</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>631591</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6663910</v>
+      </c>
+      <c r="S22" t="n">
+        <v>15</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62998-2025 artfynd.xlsx
+++ b/artfynd/A 62998-2025 artfynd.xlsx
@@ -1925,7 +1925,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130236801</v>
+        <v>130236752</v>
       </c>
       <c r="B13" t="n">
         <v>97079</v>
@@ -1960,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>631418</v>
+        <v>631701</v>
       </c>
       <c r="R13" t="n">
-        <v>6663846</v>
+        <v>6663882</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1985,7 +1985,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
@@ -2022,7 +2022,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130236752</v>
+        <v>130236801</v>
       </c>
       <c r="B14" t="n">
         <v>97079</v>
@@ -2057,10 +2057,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631701</v>
+        <v>631418</v>
       </c>
       <c r="R14" t="n">
-        <v>6663882</v>
+        <v>6663846</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Jumkil</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2119,32 +2119,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130236815</v>
+        <v>130236800</v>
       </c>
       <c r="B15" t="n">
-        <v>96322</v>
+        <v>97079</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631419</v>
+        <v>631428</v>
       </c>
       <c r="R15" t="n">
-        <v>6663842</v>
+        <v>6663768</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2216,32 +2216,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130236800</v>
+        <v>130236815</v>
       </c>
       <c r="B16" t="n">
-        <v>97079</v>
+        <v>96322</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631428</v>
+        <v>631419</v>
       </c>
       <c r="R16" t="n">
-        <v>6663768</v>
+        <v>6663842</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 62998-2025 artfynd.xlsx
+++ b/artfynd/A 62998-2025 artfynd.xlsx
@@ -1729,7 +1729,7 @@
         <v>130236804</v>
       </c>
       <c r="B11" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>130236802</v>
       </c>
       <c r="B12" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>130236752</v>
       </c>
       <c r="B13" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>130236801</v>
       </c>
       <c r="B14" t="n">
-        <v>97079</v>
+        <v>97166</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,32 +2119,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130236800</v>
+        <v>130236815</v>
       </c>
       <c r="B15" t="n">
-        <v>97079</v>
+        <v>96409</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631428</v>
+        <v>631419</v>
       </c>
       <c r="R15" t="n">
-        <v>6663768</v>
+        <v>6663842</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2216,32 +2216,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130236815</v>
+        <v>130236800</v>
       </c>
       <c r="B16" t="n">
-        <v>96322</v>
+        <v>97166</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631419</v>
+        <v>631428</v>
       </c>
       <c r="R16" t="n">
-        <v>6663842</v>
+        <v>6663768</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2316,7 +2316,7 @@
         <v>130236805</v>
       </c>
       <c r="B17" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>130236810</v>
       </c>
       <c r="B18" t="n">
-        <v>105900</v>
+        <v>105987</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>130236808</v>
       </c>
       <c r="B19" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>130236809</v>
       </c>
       <c r="B20" t="n">
-        <v>91023</v>
+        <v>91110</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,10 +2706,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236806</v>
+        <v>130236807</v>
       </c>
       <c r="B21" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631465</v>
+        <v>631591</v>
       </c>
       <c r="R21" t="n">
-        <v>6663897</v>
+        <v>6663910</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2803,10 +2803,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236807</v>
+        <v>130236806</v>
       </c>
       <c r="B22" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631591</v>
+        <v>631465</v>
       </c>
       <c r="R22" t="n">
-        <v>6663910</v>
+        <v>6663897</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Jumkil</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">

--- a/artfynd/A 62998-2025 artfynd.xlsx
+++ b/artfynd/A 62998-2025 artfynd.xlsx
@@ -2706,7 +2706,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236807</v>
+        <v>130236806</v>
       </c>
       <c r="B21" t="n">
         <v>57823</v>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631591</v>
+        <v>631465</v>
       </c>
       <c r="R21" t="n">
-        <v>6663910</v>
+        <v>6663897</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Jumkil</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2803,7 +2803,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236806</v>
+        <v>130236807</v>
       </c>
       <c r="B22" t="n">
         <v>57823</v>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631465</v>
+        <v>631591</v>
       </c>
       <c r="R22" t="n">
-        <v>6663897</v>
+        <v>6663910</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">

--- a/artfynd/A 62998-2025 artfynd.xlsx
+++ b/artfynd/A 62998-2025 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>130236752</v>
       </c>
       <c r="B13" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>130236801</v>
       </c>
       <c r="B14" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>130236800</v>
       </c>
       <c r="B15" t="n">
-        <v>97166</v>
+        <v>97169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>130236815</v>
       </c>
       <c r="B16" t="n">
-        <v>96409</v>
+        <v>96412</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>130236810</v>
       </c>
       <c r="B18" t="n">
-        <v>105987</v>
+        <v>105990</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>130236808</v>
       </c>
       <c r="B19" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>130236809</v>
       </c>
       <c r="B20" t="n">
-        <v>91110</v>
+        <v>91113</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236806</v>
+        <v>130236807</v>
       </c>
       <c r="B21" t="n">
         <v>57823</v>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631465</v>
+        <v>631591</v>
       </c>
       <c r="R21" t="n">
-        <v>6663897</v>
+        <v>6663910</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2803,7 +2803,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236807</v>
+        <v>130236806</v>
       </c>
       <c r="B22" t="n">
         <v>57823</v>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631591</v>
+        <v>631465</v>
       </c>
       <c r="R22" t="n">
-        <v>6663910</v>
+        <v>6663897</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Jumkil</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">

--- a/artfynd/A 62998-2025 artfynd.xlsx
+++ b/artfynd/A 62998-2025 artfynd.xlsx
@@ -1729,7 +1729,7 @@
         <v>130236804</v>
       </c>
       <c r="B11" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>130236802</v>
       </c>
       <c r="B12" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>130236752</v>
       </c>
       <c r="B13" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>130236801</v>
       </c>
       <c r="B14" t="n">
-        <v>97169</v>
+        <v>97195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,32 +2119,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130236800</v>
+        <v>130236815</v>
       </c>
       <c r="B15" t="n">
-        <v>97169</v>
+        <v>96438</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631428</v>
+        <v>631419</v>
       </c>
       <c r="R15" t="n">
-        <v>6663768</v>
+        <v>6663842</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2216,32 +2216,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130236815</v>
+        <v>130236800</v>
       </c>
       <c r="B16" t="n">
-        <v>96412</v>
+        <v>97195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631419</v>
+        <v>631428</v>
       </c>
       <c r="R16" t="n">
-        <v>6663842</v>
+        <v>6663768</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2316,7 +2316,7 @@
         <v>130236805</v>
       </c>
       <c r="B17" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>130236810</v>
       </c>
       <c r="B18" t="n">
-        <v>105990</v>
+        <v>106016</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>130236808</v>
       </c>
       <c r="B19" t="n">
-        <v>98923</v>
+        <v>98949</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>130236809</v>
       </c>
       <c r="B20" t="n">
-        <v>91113</v>
+        <v>91139</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>130236807</v>
       </c>
       <c r="B21" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>130236806</v>
       </c>
       <c r="B22" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 62998-2025 artfynd.xlsx
+++ b/artfynd/A 62998-2025 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>130236752</v>
       </c>
       <c r="B13" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>130236801</v>
       </c>
       <c r="B14" t="n">
-        <v>97195</v>
+        <v>97196</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,32 +2119,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130236815</v>
+        <v>130236800</v>
       </c>
       <c r="B15" t="n">
-        <v>96438</v>
+        <v>97196</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631419</v>
+        <v>631428</v>
       </c>
       <c r="R15" t="n">
-        <v>6663842</v>
+        <v>6663768</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2216,32 +2216,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130236800</v>
+        <v>130236815</v>
       </c>
       <c r="B16" t="n">
-        <v>97195</v>
+        <v>96439</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631428</v>
+        <v>631419</v>
       </c>
       <c r="R16" t="n">
-        <v>6663768</v>
+        <v>6663842</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2413,7 +2413,7 @@
         <v>130236810</v>
       </c>
       <c r="B18" t="n">
-        <v>106016</v>
+        <v>106017</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>130236808</v>
       </c>
       <c r="B19" t="n">
-        <v>98949</v>
+        <v>98950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>130236809</v>
       </c>
       <c r="B20" t="n">
-        <v>91139</v>
+        <v>91140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236807</v>
+        <v>130236806</v>
       </c>
       <c r="B21" t="n">
         <v>57849</v>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631591</v>
+        <v>631465</v>
       </c>
       <c r="R21" t="n">
-        <v>6663910</v>
+        <v>6663897</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Jumkil</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2803,7 +2803,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236806</v>
+        <v>130236807</v>
       </c>
       <c r="B22" t="n">
         <v>57849</v>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631465</v>
+        <v>631591</v>
       </c>
       <c r="R22" t="n">
-        <v>6663897</v>
+        <v>6663910</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">

--- a/artfynd/A 62998-2025 artfynd.xlsx
+++ b/artfynd/A 62998-2025 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>130236752</v>
       </c>
       <c r="B13" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>130236801</v>
       </c>
       <c r="B14" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>130236800</v>
       </c>
       <c r="B15" t="n">
-        <v>97196</v>
+        <v>97197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>130236815</v>
       </c>
       <c r="B16" t="n">
-        <v>96439</v>
+        <v>96440</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>130236810</v>
       </c>
       <c r="B18" t="n">
-        <v>106017</v>
+        <v>106018</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>130236808</v>
       </c>
       <c r="B19" t="n">
-        <v>98950</v>
+        <v>98951</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>130236809</v>
       </c>
       <c r="B20" t="n">
-        <v>91140</v>
+        <v>91141</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 62998-2025 artfynd.xlsx
+++ b/artfynd/A 62998-2025 artfynd.xlsx
@@ -1729,7 +1729,7 @@
         <v>130236804</v>
       </c>
       <c r="B11" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         <v>130236802</v>
       </c>
       <c r="B12" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1928,7 +1928,7 @@
         <v>130236752</v>
       </c>
       <c r="B13" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>130236801</v>
       </c>
       <c r="B14" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>130236800</v>
       </c>
       <c r="B15" t="n">
-        <v>97197</v>
+        <v>97199</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2219,7 +2219,7 @@
         <v>130236815</v>
       </c>
       <c r="B16" t="n">
-        <v>96440</v>
+        <v>96442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2316,7 +2316,7 @@
         <v>130236805</v>
       </c>
       <c r="B17" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2413,7 +2413,7 @@
         <v>130236810</v>
       </c>
       <c r="B18" t="n">
-        <v>106018</v>
+        <v>106020</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>130236808</v>
       </c>
       <c r="B19" t="n">
-        <v>98951</v>
+        <v>98953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2612,7 +2612,7 @@
         <v>130236809</v>
       </c>
       <c r="B20" t="n">
-        <v>91141</v>
+        <v>91143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2709,7 +2709,7 @@
         <v>130236806</v>
       </c>
       <c r="B21" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2806,7 +2806,7 @@
         <v>130236807</v>
       </c>
       <c r="B22" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 62998-2025 artfynd.xlsx
+++ b/artfynd/A 62998-2025 artfynd.xlsx
@@ -1928,7 +1928,7 @@
         <v>130236752</v>
       </c>
       <c r="B13" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2025,7 +2025,7 @@
         <v>130236801</v>
       </c>
       <c r="B14" t="n">
-        <v>97199</v>
+        <v>97203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2119,32 +2119,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130236800</v>
+        <v>130236815</v>
       </c>
       <c r="B15" t="n">
-        <v>97199</v>
+        <v>96446</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631428</v>
+        <v>631419</v>
       </c>
       <c r="R15" t="n">
-        <v>6663768</v>
+        <v>6663842</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2216,32 +2216,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130236815</v>
+        <v>130236800</v>
       </c>
       <c r="B16" t="n">
-        <v>96442</v>
+        <v>97203</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631419</v>
+        <v>631428</v>
       </c>
       <c r="R16" t="n">
-        <v>6663842</v>
+        <v>6663768</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2413,7 +2413,7 @@
         <v>130236810</v>
       </c>
       <c r="B18" t="n">
-        <v>106020</v>
+        <v>106024</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2510,7 +2510,7 @@
         <v>130236808</v>
       </c>
       <c r="B19" t="n">
-        <v>98953</v>
+        <v>98957</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236806</v>
+        <v>130236807</v>
       </c>
       <c r="B21" t="n">
         <v>57851</v>
@@ -2741,10 +2741,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631465</v>
+        <v>631591</v>
       </c>
       <c r="R21" t="n">
-        <v>6663897</v>
+        <v>6663910</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2766,7 +2766,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2803,7 +2803,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236807</v>
+        <v>130236806</v>
       </c>
       <c r="B22" t="n">
         <v>57851</v>
@@ -2838,10 +2838,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631591</v>
+        <v>631465</v>
       </c>
       <c r="R22" t="n">
-        <v>6663910</v>
+        <v>6663897</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2863,7 +2863,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Jumkil</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">

--- a/artfynd/A 62998-2025 artfynd.xlsx
+++ b/artfynd/A 62998-2025 artfynd.xlsx
@@ -2119,32 +2119,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130236815</v>
+        <v>130236800</v>
       </c>
       <c r="B15" t="n">
-        <v>96446</v>
+        <v>97203</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2170</v>
+        <v>53</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2154,10 +2154,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631419</v>
+        <v>631428</v>
       </c>
       <c r="R15" t="n">
-        <v>6663842</v>
+        <v>6663768</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2216,32 +2216,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130236800</v>
+        <v>130236815</v>
       </c>
       <c r="B16" t="n">
-        <v>97203</v>
+        <v>96446</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>53</v>
+        <v>2170</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2251,10 +2251,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631428</v>
+        <v>631419</v>
       </c>
       <c r="R16" t="n">
-        <v>6663768</v>
+        <v>6663842</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>

--- a/artfynd/A 62998-2025 artfynd.xlsx
+++ b/artfynd/A 62998-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>4945477</v>
+        <v>130236752</v>
       </c>
       <c r="B2" t="n">
-        <v>98519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222498</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Risbo, 0,5 km NV-ut, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>631473.8140413788</v>
+        <v>631701</v>
       </c>
       <c r="R2" t="n">
-        <v>6663946.660302045</v>
+        <v>6663882</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -740,27 +735,17 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2010-09-05</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2010-09-05</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,78 +756,64 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>3037519</v>
+        <v>130236800</v>
       </c>
       <c r="B3" t="n">
-        <v>96333</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Risbo, 0,5 km NV-ut, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>631445.1663694218</v>
+        <v>631428</v>
       </c>
       <c r="R3" t="n">
-        <v>6663922.669005091</v>
+        <v>6663768</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -866,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2010-09-05</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2010-09-05</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -892,78 +853,64 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>3054978</v>
+        <v>130236801</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Husby, 0,9 km SV-ut, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>631477.9169607923</v>
+        <v>631418</v>
       </c>
       <c r="R4" t="n">
-        <v>6663929.832067148</v>
+        <v>6663846</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1013,40 +950,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1750234</v>
+        <v>123680</v>
       </c>
       <c r="B5" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,34 +977,48 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5964</v>
+        <v>210</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Husby, 0,9 km SV-ut, Upl</t>
+          <t>Husby, 0,8 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>631492.5616105398</v>
+        <v>631608</v>
       </c>
       <c r="R5" t="n">
-        <v>6663953.821667706</v>
+        <v>6663989</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1103,7 +1040,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
@@ -1111,21 +1048,11 @@
           <t>2011-10-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2011-10-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1138,6 +1065,11 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>död ved</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1159,15 +1091,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3426257</v>
+        <v>190221</v>
       </c>
       <c r="B6" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98215</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1175,34 +1102,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221144</v>
+        <v>569</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Granbräken</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryopteris cristata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Husby, 0,9 km SV-ut, Upl</t>
+          <t>Husby, 0,8 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>631477.9169607923</v>
+        <v>631545</v>
       </c>
       <c r="R6" t="n">
-        <v>6663929.832067148</v>
+        <v>6663994</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1224,7 +1151,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
@@ -1232,19 +1159,9 @@
           <t>2011-10-08</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1280,50 +1197,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1340630</v>
+        <v>393604</v>
       </c>
       <c r="B7" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4769</v>
+        <v>1209</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Husby, 0,8 km SV-ut, Upl</t>
+          <t>Husby, 1,2 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>631578.2898066404</v>
+        <v>631435</v>
       </c>
       <c r="R7" t="n">
-        <v>6663975.86288412</v>
+        <v>6663558</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1257,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Jumkil</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1353,21 +1265,11 @@
           <t>2011-10-08</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2011-10-08</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1377,9 +1279,14 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Granskog</t>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>granskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>granlåga</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1401,15 +1308,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1160430</v>
+        <v>130236815</v>
       </c>
       <c r="B8" t="n">
-        <v>89170</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,37 +1319,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>3215</v>
+        <v>2170</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rödgul trumpetsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Craterellus lutescens</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fr.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Husby, 0,8 km SV-ut, Upl</t>
+          <t>Risboskogen, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>631575.0609156948</v>
+        <v>631419</v>
       </c>
       <c r="R8" t="n">
-        <v>6663982.237654466</v>
+        <v>6663842</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,27 +1368,17 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Jumkil</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2011-10-08</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,35 +1389,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Granskog</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Henry Åkerström</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
-        </is>
-      </c>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124302060</v>
+        <v>130236758</v>
       </c>
       <c r="B9" t="n">
-        <v>105293</v>
+        <v>96458</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,21 +1416,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221144</v>
+        <v>2818</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1557,13 +1440,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>631481</v>
+        <v>631702</v>
       </c>
       <c r="R9" t="n">
-        <v>6663922</v>
+        <v>6663884</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,27 +1465,17 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-21</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2025-12-20</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1617,22 +1490,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Vilhelm Kroon</t>
+          <t>Tomas Falk</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130236817</v>
+        <v>1160430</v>
       </c>
       <c r="B10" t="n">
-        <v>5177</v>
+        <v>91680</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1640,37 +1513,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Husby, 0,8 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>631422</v>
+        <v>631575</v>
       </c>
       <c r="R10" t="n">
-        <v>6663828</v>
+        <v>6663982</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1689,17 +1562,17 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1710,64 +1583,73 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130236804</v>
+        <v>1340630</v>
       </c>
       <c r="B11" t="n">
-        <v>57851</v>
+        <v>92869</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>4769</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Husby, 0,8 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>631498</v>
+        <v>631578</v>
       </c>
       <c r="R11" t="n">
-        <v>6663817</v>
+        <v>6663976</v>
       </c>
       <c r="S11" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1786,17 +1668,17 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1807,48 +1689,57 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130236802</v>
+        <v>130236809</v>
       </c>
       <c r="B12" t="n">
-        <v>57851</v>
+        <v>91282</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>5685</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1858,10 +1749,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>631483</v>
+        <v>631421</v>
       </c>
       <c r="R12" t="n">
-        <v>6663930</v>
+        <v>6663766</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1894,11 +1785,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Flykt och lockläte</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1925,10 +1811,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130236752</v>
+        <v>1750234</v>
       </c>
       <c r="B13" t="n">
-        <v>97203</v>
+        <v>93233</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1936,37 +1822,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>53</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Husby, 0,9 km SV-ut, Upl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>631701</v>
+        <v>631493</v>
       </c>
       <c r="R13" t="n">
-        <v>6663882</v>
+        <v>6663954</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1985,17 +1871,17 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Jumkil</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2011-10-08</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2006,26 +1892,35 @@
       </c>
       <c r="AG13" t="b">
         <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130236801</v>
+        <v>1750739</v>
       </c>
       <c r="B14" t="n">
-        <v>97203</v>
+        <v>93233</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2033,37 +1928,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>53</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Risbo, 0,4 km V-ut, Upl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>631418</v>
+        <v>631421</v>
       </c>
       <c r="R14" t="n">
-        <v>6663846</v>
+        <v>6663528</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2087,12 +1982,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2012-09-02</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2012-09-02</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2103,64 +1998,69 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130236800</v>
+        <v>1892805</v>
       </c>
       <c r="B15" t="n">
-        <v>97203</v>
+        <v>80336</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>53</v>
+        <v>6456</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Risbo, 0,5 km NV-ut, Upl</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>631428</v>
+        <v>631406</v>
       </c>
       <c r="R15" t="n">
-        <v>6663768</v>
+        <v>6663868</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2184,12 +2084,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2010-09-05</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2010-09-05</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2200,26 +2100,40 @@
       </c>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>aspbark</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
+          <t>Henry Åkerström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Falk</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130236815</v>
+        <v>130236802</v>
       </c>
       <c r="B16" t="n">
-        <v>96446</v>
+        <v>57950</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2227,21 +2141,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2251,10 +2165,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>631419</v>
+        <v>631483</v>
       </c>
       <c r="R16" t="n">
-        <v>6663842</v>
+        <v>6663930</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2287,6 +2201,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flykt och lockläte</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2313,14 +2232,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130236805</v>
+        <v>130236804</v>
       </c>
       <c r="B17" t="n">
-        <v>57851</v>
+        <v>57950</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2348,10 +2267,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>631493</v>
+        <v>631498</v>
       </c>
       <c r="R17" t="n">
-        <v>6663935</v>
+        <v>6663817</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2410,10 +2329,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130236810</v>
+        <v>130236805</v>
       </c>
       <c r="B18" t="n">
-        <v>106024</v>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2421,21 +2340,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221144</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2445,10 +2364,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>631475</v>
+        <v>631493</v>
       </c>
       <c r="R18" t="n">
-        <v>6663922</v>
+        <v>6663935</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2507,32 +2426,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130236808</v>
+        <v>130236806</v>
       </c>
       <c r="B19" t="n">
-        <v>98957</v>
+        <v>57950</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2542,10 +2461,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>631477</v>
+        <v>631465</v>
       </c>
       <c r="R19" t="n">
-        <v>6663923</v>
+        <v>6663897</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2578,11 +2497,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>18 buketter</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2609,10 +2523,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130236809</v>
+        <v>130236807</v>
       </c>
       <c r="B20" t="n">
-        <v>91143</v>
+        <v>57950</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2620,21 +2534,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5685</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2644,10 +2558,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>631421</v>
+        <v>631591</v>
       </c>
       <c r="R20" t="n">
-        <v>6663766</v>
+        <v>6663910</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2669,7 +2583,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>Jumkil</t>
+          <t>Bälinge</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
@@ -2706,32 +2620,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130236807</v>
+        <v>130236817</v>
       </c>
       <c r="B21" t="n">
-        <v>57851</v>
+        <v>5179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>100526</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2741,10 +2655,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>631591</v>
+        <v>631422</v>
       </c>
       <c r="R21" t="n">
-        <v>6663910</v>
+        <v>6663828</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2766,7 +2680,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Bälinge</t>
+          <t>Jumkil</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
@@ -2803,48 +2717,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130236806</v>
+        <v>3037519</v>
       </c>
       <c r="B22" t="n">
-        <v>57851</v>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Risboskogen, Upl</t>
+          <t>Risbo, 0,5 km NV-ut, Upl</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>631465</v>
+        <v>631445</v>
       </c>
       <c r="R22" t="n">
-        <v>6663897</v>
+        <v>6663923</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2868,12 +2782,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2010-09-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-12-20</t>
+          <t>2010-09-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2884,19 +2798,1068 @@
       </c>
       <c r="AG22" t="b">
         <v>0</v>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
       </c>
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>3054978</v>
+      </c>
+      <c r="B23" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Husby, 0,9 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>631478</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6663930</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2011-10-08</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2011-10-08</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>130236808</v>
+      </c>
+      <c r="B24" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>631477</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6663923</v>
+      </c>
+      <c r="S24" t="n">
+        <v>15</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>18 buketter</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
+      <c r="AX24" t="inlineStr">
         <is>
           <t>Tomas Falk</t>
         </is>
       </c>
-      <c r="AY22" t="inlineStr"/>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>3426257</v>
+      </c>
+      <c r="B25" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Husby, 0,9 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>631478</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6663930</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2011-10-08</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2011-10-08</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>124302060</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>631481</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6663922</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-04-21</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Vilhelm Kroon</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>130236810</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106243</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Risboskogen, Upl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>631475</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6663922</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Tomas Falk</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>4945477</v>
+      </c>
+      <c r="B28" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Risbo, 0,5 km NV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>631474</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6663947</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2010-09-05</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2010-09-05</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>4955708</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Husby, 0,8 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>631608</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6663989</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2011-10-08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2011-10-08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>4955709</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Husby, 1,2 km SV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>631435</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6663558</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2011-10-08</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2011-10-08</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>4963619</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Risbo, 0,3 km V-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>631432</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6663567</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Jumkil</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2012-09-02</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2012-09-02</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>5983095</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Risbo, 0,5 km NV-ut, Upl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>631509</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6663970</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Bälinge</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2010-09-05</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2010-09-05</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Henry Åkerström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen Uppsala, skogsgruppexkursion</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
